--- a/shadow-app/public/test fust invoice.xlsx
+++ b/shadow-app/public/test fust invoice.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vdvfi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vdvfi\SynologyDrive\SnappySjaak\shadow-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9FCD6F-0A0C-4B45-9760-07A11A17BC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32248F0-AEBE-4D76-A8B5-BD6E11F37478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-72120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,9 +59,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;€&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
-    <numFmt numFmtId="167" formatCode="\€#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="\€#,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -124,6 +124,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -139,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -162,11 +168,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -183,100 +269,17 @@
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -286,6 +289,81 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -581,7 +659,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P114"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr defaultColWidth="11.85546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="7" width="11.85546875" style="3"/>
@@ -595,479 +673,412 @@
     <row r="10" spans="2:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="2:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="12" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="I12" s="50" t="s">
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="I12" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="45"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
     </row>
     <row r="13" spans="2:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="5"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
     </row>
     <row r="14" spans="2:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="39" t="s">
         <v>3</v>
       </c>
       <c r="H14" s="7"/>
-      <c r="I14" s="44"/>
+      <c r="I14" s="12"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
     </row>
     <row r="15" spans="2:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="2:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:16" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="48" t="s">
+    <row r="17" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="17" t="s">
         <v>2</v>
       </c>
       <c r="C17" s="6"/>
-      <c r="N17" s="51" t="s">
+      <c r="E17" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="O17" s="52"/>
-      <c r="P17" s="52" t="s">
+      <c r="F17" s="21"/>
+      <c r="G17" s="21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="14"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="16"/>
-    </row>
-    <row r="19" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="46">
+    <row r="18" spans="2:12" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="13"/>
+      <c r="D18" s="14"/>
+      <c r="F18"/>
+      <c r="G18"/>
+    </row>
+    <row r="19" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="15">
         <v>510</v>
       </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="39"/>
-      <c r="N19" s="23"/>
-      <c r="P19" s="23"/>
-    </row>
-    <row r="20" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="47"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="39"/>
-    </row>
-    <row r="21" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="47"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="41"/>
-    </row>
-    <row r="22" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="46">
+      <c r="C19" s="23"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="10"/>
+      <c r="F19"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="26"/>
+    </row>
+    <row r="20" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="16"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="26"/>
+    </row>
+    <row r="21" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="16"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="26"/>
+    </row>
+    <row r="22" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="15">
         <v>519</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="N22" s="23"/>
-      <c r="P22" s="23"/>
-    </row>
-    <row r="23" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="47"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="26"/>
-      <c r="L23" s="28"/>
-    </row>
-    <row r="24" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="47"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="12"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="13"/>
-    </row>
-    <row r="25" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="46">
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="10"/>
+      <c r="F22"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+    </row>
+    <row r="23" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="16"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="29"/>
+    </row>
+    <row r="24" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="16"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="29"/>
+    </row>
+    <row r="25" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="15">
         <v>520</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="28"/>
-      <c r="N25" s="23"/>
-      <c r="P25" s="23"/>
-    </row>
-    <row r="26" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="47"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="28"/>
-    </row>
-    <row r="27" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="47"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="13"/>
-    </row>
-    <row r="28" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="46">
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="10"/>
+      <c r="F25"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="29"/>
+    </row>
+    <row r="26" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="16"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="29"/>
+    </row>
+    <row r="27" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="16"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="29"/>
+    </row>
+    <row r="28" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="15">
         <v>525</v>
       </c>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="26"/>
-      <c r="L28" s="28"/>
-      <c r="N28" s="23"/>
-      <c r="P28" s="23"/>
-    </row>
-    <row r="29" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="47"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="28"/>
-    </row>
-    <row r="30" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="47"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="13"/>
-    </row>
-    <row r="31" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="46">
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="10"/>
+      <c r="F28"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="29"/>
+    </row>
+    <row r="29" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="16"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="29"/>
+    </row>
+    <row r="30" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="16"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="28"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="29"/>
+    </row>
+    <row r="31" spans="2:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="15">
         <v>533</v>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="39"/>
-      <c r="N31" s="23"/>
-      <c r="P31" s="23"/>
-    </row>
-    <row r="32" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="47"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="10"/>
+      <c r="F31"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="26"/>
+    </row>
+    <row r="32" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="16"/>
       <c r="C32" s="30"/>
       <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
       <c r="H32" s="30"/>
       <c r="I32" s="30"/>
       <c r="J32" s="30"/>
       <c r="K32" s="30"/>
       <c r="L32" s="30"/>
     </row>
-    <row r="33" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="19"/>
-    </row>
-    <row r="34" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="16"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="32"/>
+    </row>
+    <row r="34" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="B34" s="46">
+      <c r="B34" s="15">
         <v>544</v>
       </c>
       <c r="C34" s="30"/>
       <c r="D34" s="30"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
+      <c r="E34" s="11"/>
+      <c r="G34" s="11"/>
       <c r="H34" s="33"/>
       <c r="I34" s="35"/>
       <c r="J34" s="34"/>
       <c r="K34" s="33"/>
       <c r="L34" s="35"/>
-      <c r="N34" s="29"/>
-      <c r="P34" s="29"/>
-    </row>
-    <row r="35" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="47"/>
+      <c r="B35" s="16"/>
       <c r="C35" s="30"/>
       <c r="D35" s="30"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
       <c r="H35" s="33"/>
       <c r="I35" s="35"/>
       <c r="J35" s="34"/>
       <c r="K35" s="33"/>
       <c r="L35" s="35"/>
     </row>
-    <row r="36" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="21"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="22"/>
-    </row>
-    <row r="37" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="16"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="35"/>
+    </row>
+    <row r="37" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="46">
+      <c r="B37" s="15">
         <v>560</v>
       </c>
       <c r="C37" s="30"/>
       <c r="D37" s="30"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
+      <c r="E37" s="11"/>
+      <c r="G37" s="11"/>
       <c r="H37" s="33"/>
       <c r="I37" s="35"/>
       <c r="J37" s="34"/>
       <c r="K37" s="33"/>
       <c r="L37" s="35"/>
-      <c r="N37" s="29"/>
-      <c r="P37" s="29"/>
-    </row>
-    <row r="38" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="47"/>
+      <c r="B38" s="16"/>
       <c r="C38" s="30"/>
       <c r="D38" s="30"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
       <c r="H38" s="33"/>
       <c r="I38" s="35"/>
       <c r="J38" s="34"/>
       <c r="K38" s="33"/>
       <c r="L38" s="35"/>
     </row>
-    <row r="39" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="21"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="22"/>
-    </row>
-    <row r="40" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="16"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="35"/>
+    </row>
+    <row r="40" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="B40" s="46">
+      <c r="B40" s="15">
         <v>566</v>
       </c>
       <c r="C40" s="30"/>
       <c r="D40" s="30"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
+      <c r="E40" s="11"/>
+      <c r="G40" s="11"/>
       <c r="H40" s="33"/>
       <c r="I40" s="35"/>
       <c r="J40" s="34"/>
       <c r="K40" s="33"/>
       <c r="L40" s="35"/>
-      <c r="N40" s="29"/>
-      <c r="P40" s="29"/>
-    </row>
-    <row r="41" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="47"/>
+    </row>
+    <row r="41" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="16"/>
       <c r="C41" s="30"/>
       <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
       <c r="H41" s="30"/>
       <c r="I41" s="32"/>
       <c r="J41" s="30"/>
       <c r="K41" s="30"/>
       <c r="L41" s="32"/>
     </row>
-    <row r="42" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="47"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="17"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="19"/>
-    </row>
-    <row r="43" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="46">
+    <row r="42" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="16"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="32"/>
+    </row>
+    <row r="43" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="15">
         <v>577</v>
       </c>
       <c r="C43" s="30"/>
       <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
+      <c r="E43" s="11"/>
+      <c r="G43" s="11"/>
       <c r="H43" s="30"/>
       <c r="I43" s="32"/>
       <c r="J43" s="30"/>
       <c r="K43" s="30"/>
       <c r="L43" s="32"/>
-      <c r="N43" s="29"/>
-      <c r="P43" s="29"/>
-    </row>
-    <row r="44" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="47"/>
+    </row>
+    <row r="44" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="16"/>
       <c r="C44" s="30"/>
       <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
       <c r="H44" s="30"/>
       <c r="I44" s="32"/>
       <c r="J44" s="31"/>
       <c r="K44" s="30"/>
       <c r="L44" s="32"/>
     </row>
-    <row r="45" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="47"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="19"/>
-    </row>
-    <row r="46" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="46">
+    <row r="45" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="16"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="32"/>
+    </row>
+    <row r="46" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="15">
         <v>596</v>
       </c>
       <c r="C46" s="30"/>
       <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
+      <c r="E46" s="11"/>
+      <c r="G46" s="11"/>
       <c r="H46" s="30"/>
       <c r="I46" s="32"/>
       <c r="J46" s="31"/>
       <c r="K46" s="30"/>
       <c r="L46" s="32"/>
-      <c r="N46" s="29"/>
-      <c r="P46" s="29"/>
-    </row>
-    <row r="47" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="47"/>
+    </row>
+    <row r="47" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="16"/>
       <c r="C47" s="30"/>
       <c r="D47" s="30"/>
       <c r="E47" s="30"/>
@@ -1079,371 +1090,413 @@
       <c r="K47" s="30"/>
       <c r="L47" s="32"/>
     </row>
-    <row r="48" spans="1:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="47"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="18"/>
-      <c r="G48" s="18"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="18"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="19"/>
-    </row>
-    <row r="49" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="46">
+    <row r="48" spans="1:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="16"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="32"/>
+    </row>
+    <row r="49" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="15">
         <v>597</v>
       </c>
       <c r="C49" s="30"/>
       <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
+      <c r="E49" s="11"/>
+      <c r="G49" s="11"/>
       <c r="H49" s="30"/>
       <c r="I49" s="32"/>
       <c r="J49" s="31"/>
       <c r="K49" s="30"/>
       <c r="L49" s="32"/>
-      <c r="N49" s="29"/>
-      <c r="P49" s="29"/>
-    </row>
-    <row r="50" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="47"/>
+    </row>
+    <row r="50" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="16"/>
       <c r="C50" s="30"/>
       <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
       <c r="H50" s="30"/>
       <c r="I50" s="32"/>
       <c r="J50" s="31"/>
       <c r="K50" s="30"/>
       <c r="L50" s="32"/>
     </row>
-    <row r="51" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="47"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="18"/>
-      <c r="H51" s="17"/>
-      <c r="I51" s="19"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="19"/>
-    </row>
-    <row r="52" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="46" t="s">
+    <row r="51" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="16"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="32"/>
+    </row>
+    <row r="52" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="30"/>
       <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="31"/>
+      <c r="E52" s="11"/>
+      <c r="G52" s="11"/>
       <c r="H52" s="30"/>
       <c r="I52" s="32"/>
       <c r="J52" s="31"/>
       <c r="K52" s="30"/>
       <c r="L52" s="32"/>
-      <c r="N52" s="29"/>
-      <c r="P52" s="29"/>
-    </row>
-    <row r="53" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="47"/>
+    </row>
+    <row r="53" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="16"/>
       <c r="C53" s="30"/>
       <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="31"/>
-      <c r="G53" s="31"/>
       <c r="H53" s="30"/>
       <c r="I53" s="32"/>
       <c r="J53" s="31"/>
       <c r="K53" s="30"/>
       <c r="L53" s="32"/>
     </row>
-    <row r="54" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="47"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="17"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="18"/>
-      <c r="K54" s="17"/>
-      <c r="L54" s="19"/>
-    </row>
-    <row r="55" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="46" t="s">
+    <row r="54" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="16"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="31"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="32"/>
+    </row>
+    <row r="55" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="15" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="30"/>
       <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
+      <c r="E55" s="11"/>
+      <c r="G55" s="11"/>
       <c r="H55" s="30"/>
       <c r="I55" s="32"/>
       <c r="J55" s="31"/>
       <c r="K55" s="30"/>
       <c r="L55" s="32"/>
-      <c r="N55" s="29"/>
-      <c r="P55" s="29"/>
-    </row>
-    <row r="56" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="47"/>
+    </row>
+    <row r="56" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="16"/>
       <c r="C56" s="30"/>
       <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="31"/>
       <c r="H56" s="30"/>
       <c r="I56" s="32"/>
       <c r="J56" s="31"/>
       <c r="K56" s="30"/>
       <c r="L56" s="32"/>
     </row>
-    <row r="57" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="47"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="17"/>
-      <c r="I57" s="19"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="17"/>
-      <c r="L57" s="19"/>
-    </row>
-    <row r="58" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="46" t="s">
+    <row r="57" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="16"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="31"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="32"/>
+    </row>
+    <row r="58" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="30"/>
       <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
+      <c r="E58" s="11"/>
+      <c r="G58" s="11"/>
       <c r="H58" s="30"/>
       <c r="I58" s="32"/>
       <c r="J58" s="31"/>
       <c r="K58" s="30"/>
       <c r="L58" s="32"/>
-      <c r="N58" s="29"/>
-      <c r="P58" s="29"/>
-    </row>
-    <row r="59" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="47"/>
+    </row>
+    <row r="59" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="16"/>
       <c r="C59" s="30"/>
       <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
       <c r="H59" s="30"/>
       <c r="I59" s="32"/>
       <c r="J59" s="31"/>
       <c r="K59" s="30"/>
       <c r="L59" s="32"/>
     </row>
-    <row r="60" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="47"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="19"/>
-    </row>
-    <row r="61" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="46" t="s">
+    <row r="60" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="16"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="32"/>
+      <c r="J60" s="31"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="32"/>
+    </row>
+    <row r="61" spans="2:12" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="36"/>
-      <c r="G61" s="36"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="37"/>
-      <c r="J61" s="36"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="37"/>
-      <c r="N61" s="29"/>
-      <c r="P61" s="29"/>
-    </row>
-    <row r="62" spans="2:16" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C62" s="29"/>
-      <c r="D62" s="29"/>
-      <c r="E62" s="29"/>
-      <c r="F62" s="36"/>
-      <c r="G62" s="36"/>
-      <c r="H62" s="29"/>
-      <c r="I62" s="37"/>
-      <c r="J62" s="36"/>
-      <c r="K62" s="29"/>
-      <c r="L62" s="37"/>
-    </row>
-    <row r="63" spans="2:16" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="I63" s="9"/>
-    </row>
-    <row r="64" spans="2:16" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="I64" s="9"/>
-    </row>
-    <row r="65" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="I65" s="9"/>
-    </row>
-    <row r="66" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="I66" s="9"/>
-    </row>
-    <row r="67" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="I67" s="9"/>
-    </row>
-    <row r="68" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="I68" s="9"/>
-    </row>
-    <row r="69" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="I69" s="9"/>
-    </row>
-    <row r="70" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="I70" s="9"/>
-    </row>
-    <row r="71" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="I71" s="9"/>
-    </row>
-    <row r="72" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="I72" s="9"/>
-    </row>
-    <row r="73" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="I73" s="9"/>
-    </row>
-    <row r="74" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C61" s="36"/>
+      <c r="D61" s="36"/>
+      <c r="E61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="36"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="37"/>
+      <c r="K61" s="36"/>
+      <c r="L61" s="38"/>
+    </row>
+    <row r="62" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C62" s="36"/>
+      <c r="D62" s="36"/>
+      <c r="H62" s="36"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="37"/>
+      <c r="K62" s="36"/>
+      <c r="L62" s="38"/>
+    </row>
+    <row r="63" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C63" s="36"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
+      <c r="H63" s="36"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="36"/>
+      <c r="K63" s="36"/>
+      <c r="L63" s="36"/>
+    </row>
+    <row r="64" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C64" s="36"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="36"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="36"/>
+      <c r="K64" s="36"/>
+      <c r="L64" s="36"/>
+    </row>
+    <row r="65" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B65" s="41"/>
+      <c r="C65" s="42"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="43"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="42"/>
+      <c r="K65" s="43"/>
+      <c r="L65" s="36"/>
+    </row>
+    <row r="66" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B66" s="44"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="45"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="37"/>
+      <c r="H66" s="44"/>
+      <c r="I66" s="40"/>
+      <c r="J66" s="40"/>
+      <c r="K66" s="45"/>
+      <c r="L66" s="36"/>
+    </row>
+    <row r="67" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B67" s="44"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="40"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="37"/>
+      <c r="H67" s="44"/>
+      <c r="I67" s="40"/>
+      <c r="J67" s="40"/>
+      <c r="K67" s="45"/>
+      <c r="L67" s="36"/>
+    </row>
+    <row r="68" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B68" s="44"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="45"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
+      <c r="H68" s="44"/>
+      <c r="I68" s="40"/>
+      <c r="J68" s="40"/>
+      <c r="K68" s="45"/>
+      <c r="L68" s="36"/>
+    </row>
+    <row r="69" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B69" s="44"/>
+      <c r="C69" s="40"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="37"/>
+      <c r="H69" s="44"/>
+      <c r="I69" s="40"/>
+      <c r="J69" s="40"/>
+      <c r="K69" s="45"/>
+      <c r="L69" s="36"/>
+    </row>
+    <row r="70" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B70" s="44"/>
+      <c r="C70" s="40"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="45"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="37"/>
+      <c r="H70" s="44"/>
+      <c r="I70" s="40"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="45"/>
+      <c r="L70" s="36"/>
+    </row>
+    <row r="71" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="46"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="37"/>
+      <c r="H71" s="46"/>
+      <c r="I71" s="47"/>
+      <c r="J71" s="47"/>
+      <c r="K71" s="48"/>
+      <c r="L71" s="36"/>
+    </row>
+    <row r="72" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="37"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="36"/>
+      <c r="K72" s="36"/>
+      <c r="L72" s="36"/>
+    </row>
+    <row r="73" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C73" s="36"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="37"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="36"/>
+      <c r="K73" s="36"/>
+      <c r="L73" s="36"/>
+    </row>
+    <row r="74" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
       <c r="I74" s="9"/>
     </row>
-    <row r="75" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
       <c r="I75" s="9"/>
     </row>
-    <row r="76" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
       <c r="I76" s="9"/>
     </row>
-    <row r="77" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
       <c r="I77" s="9"/>
     </row>
-    <row r="78" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
       <c r="I78" s="9"/>
     </row>
-    <row r="79" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
       <c r="I79" s="9"/>
     </row>
-    <row r="80" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
       <c r="I80" s="9"/>
     </row>
-    <row r="81" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
       <c r="I81" s="9"/>
     </row>
-    <row r="82" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
       <c r="I82" s="9"/>
     </row>
-    <row r="83" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
       <c r="I83" s="9"/>
     </row>
-    <row r="84" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
       <c r="I84" s="9"/>
     </row>
-    <row r="85" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
       <c r="I85" s="9"/>
     </row>
-    <row r="86" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
       <c r="I86" s="9"/>
     </row>
-    <row r="87" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
       <c r="I87" s="9"/>
     </row>
-    <row r="88" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
       <c r="I88" s="9"/>
     </row>
-    <row r="89" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
       <c r="I89" s="9"/>
     </row>
-    <row r="90" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
       <c r="I90" s="9"/>
     </row>
-    <row r="91" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
       <c r="I91" s="9"/>
     </row>
-    <row r="92" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
       <c r="I92" s="9"/>
     </row>
-    <row r="93" spans="6:9" s="2" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="6:9" s="2" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
       <c r="I93" s="9"/>
@@ -1589,9 +1642,11 @@
       <c r="I114" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="J12:L13"/>
     <mergeCell ref="C12:D13"/>
+    <mergeCell ref="H65:K71"/>
+    <mergeCell ref="B65:E71"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId1"/>
